--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_i_peringrmin_a_2018_valparaiso.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_i_peringrmin_a_2018_valparaiso.xlsx
@@ -111,7 +111,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 13:52</t>
+    <t xml:space="preserve">2026-09-24 00:43</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -828,7 +828,7 @@
         <v>0.21</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>0.12</v>
@@ -851,7 +851,7 @@
         <v>-0.05</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>-0.05</v>
@@ -874,7 +874,7 @@
         <v>0.26</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>0.13</v>
@@ -888,7 +888,7 @@
         <v>22</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>38</v>
@@ -897,7 +897,7 @@
         <v>0.22</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>0.16</v>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_i_peringrmin_a_2018_valparaiso.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_i_peringrmin_a_2018_valparaiso.xlsx
@@ -111,7 +111,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:43</t>
+    <t xml:space="preserve">2026-10-01 23:18</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_i_peringrmin_a_2018_valparaiso.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_i_peringrmin_a_2018_valparaiso.xlsx
@@ -111,7 +111,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:18</t>
+    <t xml:space="preserve">2026-10-05 19:30</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
